--- a/reports/集团总公司_利润表_2025-05.xlsx
+++ b/reports/集团总公司_利润表_2025-05.xlsx
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>225710366</v>
+        <v>245781613</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>171688653</v>
+        <v>186591287</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>799492796</v>
+        <v>866157271</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>698032</v>
+        <v>907837</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>3253181</v>
+        <v>4222263</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>607907</v>
+        <v>792936</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>2823060</v>
+        <v>3694923</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>514049</v>
+        <v>668238</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>2390308</v>
+        <v>3118530</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>475702</v>
+        <v>615985</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>2201472</v>
+        <v>2877308</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>257620</v>
+        <v>338510</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>1195758</v>
+        <v>1581398</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>207157</v>
+        <v>266674</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>958091</v>
+        <v>1245060</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>222949899</v>
+        <v>242191433</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>168928186</v>
+        <v>183001107</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>87288084</v>
+        <v>94945787</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>405582995</v>
+        <v>442354823</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1596803</v>
+        <v>2837850</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>7438448</v>
+        <v>13155430</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1442644</v>
+        <v>2066361</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>6717329</v>
+        <v>9569012</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>76876539</v>
+        <v>81832316</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>358923579</v>
+        <v>378258260</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1652860</v>
+        <v>2069772</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>7673063</v>
+        <v>9584830</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>716677</v>
+        <v>1033499</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>3350546</v>
+        <v>4795454</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2583615</v>
+        <v>3097178</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>11984079</v>
+        <v>14397388</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1128234</v>
+        <v>1546374</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>5261205</v>
+        <v>7197504</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>53851530</v>
+        <v>53583366</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>250483425</v>
+        <v>250680675</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>170183</v>
+        <v>169423</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>849503</v>
+        <v>850883</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>3263110</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>15244548</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>2174427</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>10155715</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>163381519</v>
+        <v>184642342</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>131133746</v>
+        <v>138126076</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>103110745</v>
+        <v>110074155</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>479808476</v>
+        <v>512652811</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>28023001</v>
+        <v>28051921</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>129931490</v>
+        <v>129673256</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>5469933</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>25347203</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1752720</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>8115021</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>1096272</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>5075308</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>1315567</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>6094912</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>985993</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>4574324</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>656478</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>3051095</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>546151</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>2543187</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>3025173</v>
+        <v>3032004</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>14107884</v>
+        <v>14151244</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1436585</v>
+        <v>1429096</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>6653865</v>
+        <v>6671618</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>3700339</v>
+        <v>3692245</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>17227804</v>
+        <v>17233359</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>24050713</v>
+        <v>23917822</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>111609165</v>
+        <v>111479694</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>350867</v>
+        <v>2933220</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>1749037</v>
+        <v>13621267</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>1120681</v>
+        <v>1117861</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>5599552</v>
+        <v>5592275</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>1164306</v>
+        <v>1068570</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>5805192</v>
+        <v>5343854</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>119811</v>
+        <v>120022</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>600225</v>
+        <v>598946</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>478053</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>2381207</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>958651</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>4438263</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>319317</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>1589190</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>239471</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>1192762</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>398808</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>1989315</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>1367379</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>6356757</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>212048</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>1061827</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>158759</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>796347</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>264207</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>1326818</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>184769</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>928248</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>131943</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>662565</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>105607</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>529668</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>79295</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>397007</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3549,7 +3549,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>59568380</v>
+        <v>60882090</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>64551039</v>
+        <v>65281702</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>547212</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>2534985</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>132978</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>661786</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>209138</v>
+        <v>210873</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>1050246</v>
+        <v>1049563</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>59359242</v>
+        <v>61218429</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>7059193</v>
+        <v>7123686</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>35474308</v>
+        <v>35533086</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>52300049</v>
+        <v>54094743</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>52300049</v>
+        <v>54094743</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>52300049</v>
+        <v>54094743</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>52300049</v>
+        <v>54094743</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>52300049</v>
+        <v>54094743</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
